--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487875_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487875_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5128</v>
+        <v>3.3762</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0804</v>
+        <v>2.9732</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4324</v>
+        <v>0.403</v>
       </c>
       <c r="G2" t="n">
         <v>0.802</v>
@@ -610,13 +610,13 @@
         <v>0.8325</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8783</v>
+        <v>1.7418</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3883</v>
+        <v>1.2811</v>
       </c>
       <c r="U2" t="n">
-        <v>0.49</v>
+        <v>0.4606</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3987</v>
+        <v>2.5204</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1696</v>
+        <v>4.0858</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7709</v>
+        <v>-1.5654</v>
       </c>
       <c r="G3" t="n">
         <v>0.2244</v>
@@ -688,13 +688,13 @@
         <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.6716</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7358</v>
+        <v>0.652</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1859</v>
+        <v>0.0196</v>
       </c>
       <c r="V3" t="n">
         <v>0.5838</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.31</v>
+        <v>2.3482</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3848</v>
+        <v>2.5991</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.2509</v>
       </c>
       <c r="G4" t="n">
         <v>2.0702</v>
@@ -766,13 +766,13 @@
         <v>0.2081</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2616</v>
+        <v>0.2998</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1305</v>
+        <v>0.0838</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3921</v>
+        <v>0.216</v>
       </c>
       <c r="V4" t="n">
         <v>-0.23</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8989</v>
+        <v>1.0779</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5644</v>
+        <v>1.802</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6654</v>
+        <v>-0.7241</v>
       </c>
       <c r="G5" t="n">
         <v>2.416</v>
@@ -844,13 +844,13 @@
         <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0667</v>
+        <v>1.2456</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4129</v>
+        <v>0.6506</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6538</v>
+        <v>0.595</v>
       </c>
       <c r="V5" t="n">
         <v>-1.7513</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.6794</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1547</v>
+        <v>3.1471</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.5584</v>
+        <v>-2.4677</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2141</v>
+        <v>0.0621</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3495</v>
+        <v>0.5095</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8646</v>
+        <v>-0.4474</v>
       </c>
       <c r="J6" t="n">
-        <v>1.664</v>
+        <v>3.6712</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9978</v>
+        <v>3.4451</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6662</v>
+        <v>0.2261</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.8781</v>
+        <v>-3.6091</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3473</v>
+        <v>-2.9355</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.5308</v>
+        <v>-0.6735</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6244</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6244</v>
+        <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>1.186</v>
+        <v>1.636</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4907</v>
+        <v>1.2002</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3047</v>
+        <v>0.4358</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2046</v>
+        <v>-0.3639</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7604</v>
+        <v>2.1064</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5558</v>
+        <v>-2.4703</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0621</v>
+        <v>-1.2141</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5095</v>
+        <v>-0.3495</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4474</v>
+        <v>-0.8646</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6712</v>
+        <v>1.664</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4451</v>
+        <v>0.9978</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2261</v>
+        <v>0.6662</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.6091</v>
+        <v>-2.8781</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.9355</v>
+        <v>-1.3473</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6735</v>
+        <v>-1.5308</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8731</v>
+        <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1613</v>
+        <v>0.2259</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8135</v>
+        <v>0.4425</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3478</v>
+        <v>-0.2166</v>
       </c>
       <c r="V7" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5276</v>
+        <v>-1.557</v>
       </c>
       <c r="E8" t="n">
         <v>-0.6246</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.903</v>
+        <v>-0.9323</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4147</v>
@@ -1078,13 +1078,13 @@
         <v>1.8731</v>
       </c>
       <c r="S8" t="n">
-        <v>1.552</v>
+        <v>1.5227</v>
       </c>
       <c r="T8" t="n">
         <v>1.2049</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3471</v>
+        <v>0.3178</v>
       </c>
       <c r="V8" t="n">
         <v>0.5838</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. FRANCH DE PABLO</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0121</v>
+        <v>-1.7074</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2861</v>
+        <v>1.7522</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7261</v>
+        <v>-3.4596</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4993</v>
+        <v>-3.0965</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.292</v>
+        <v>-2.5715</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2074</v>
+        <v>-0.525</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2112</v>
+        <v>-0.6387</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6716</v>
+        <v>-1.073</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5396</v>
+        <v>0.4343</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7106</v>
+        <v>-2.4578</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9636</v>
+        <v>-1.4985</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.747</v>
+        <v>-0.9593</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6244</v>
+        <v>2.0812</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4162</v>
+        <v>2.0812</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3047</v>
+        <v>1.0592</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4567</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.152</v>
+        <v>0.4195</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5838</v>
+        <v>-1.7513</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5838</v>
+        <v>-3.5026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>J. FRANCH DE PABLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1044</v>
+        <v>-1.8728</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4727</v>
+        <v>0.0587</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.5771</v>
+        <v>-1.9316</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0965</v>
+        <v>-0.4993</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5715</v>
+        <v>-0.292</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.525</v>
+        <v>-0.2074</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6387</v>
+        <v>1.2112</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.073</v>
+        <v>0.6716</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4343</v>
+        <v>0.5396</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4578</v>
+        <v>-1.7106</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4985</v>
+        <v>-0.9636</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9593</v>
+        <v>-0.747</v>
       </c>
       <c r="P10" t="n">
-        <v>2.0812</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0812</v>
+        <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6622</v>
+        <v>-0.1654</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3601</v>
+        <v>-0.1119</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3021</v>
+        <v>-0.0535</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7513</v>
+        <v>-0.5838</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.5026</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.438</v>
+        <v>-7.0094</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1627</v>
+        <v>-2.7341</v>
       </c>
       <c r="F11" t="n">
         <v>-4.2753</v>
@@ -1312,10 +1312,10 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8077</v>
+        <v>-0.3791</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9134</v>
+        <v>-0.4848</v>
       </c>
       <c r="U11" t="n">
         <v>0.1057</v>
@@ -1345,28 +1345,28 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1608</v>
+        <v>-2.508400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>14.5136</v>
+        <v>15.1658</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.6744</v>
+        <v>-17.6742</v>
       </c>
       <c r="G12" t="n">
         <v>-5.5726</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.1645</v>
+        <v>-7.164499999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1.591899999999999</v>
+        <v>1.5919</v>
       </c>
       <c r="J12" t="n">
         <v>17.9025</v>
       </c>
       <c r="K12" t="n">
-        <v>7.779000000000001</v>
+        <v>7.779</v>
       </c>
       <c r="L12" t="n">
         <v>10.1233</v>
@@ -1381,7 +1381,7 @@
         <v>-8.531599999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.4872</v>
@@ -1390,13 +1390,13 @@
         <v>12.4872</v>
       </c>
       <c r="S12" t="n">
-        <v>7.205600000000001</v>
+        <v>7.858099999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>4.9056</v>
+        <v>5.558</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3</v>
+        <v>2.2999</v>
       </c>
       <c r="V12" t="n">
         <v>-4.7939</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9542</v>
+        <v>5.6518</v>
       </c>
       <c r="E13" t="n">
-        <v>7.6567</v>
+        <v>7.0138</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7025</v>
+        <v>-1.362</v>
       </c>
       <c r="G13" t="n">
         <v>4.2016</v>
@@ -1468,13 +1468,13 @@
         <v>2.2893</v>
       </c>
       <c r="S13" t="n">
-        <v>0.047</v>
+        <v>-0.2554</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3849</v>
+        <v>-0.2581</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3379</v>
+        <v>0.0027</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5838</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2234</v>
+        <v>3.2568</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2997</v>
+        <v>3.7283</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0762</v>
+        <v>-0.4715</v>
       </c>
       <c r="G14" t="n">
         <v>5.4854</v>
@@ -1546,13 +1546,13 @@
         <v>1.8731</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0133</v>
+        <v>-0.9799</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8482</v>
+        <v>-0.4195</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1651</v>
+        <v>-0.5604</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. UNIACKE</t>
+          <t>A. PALAZUELOS PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0035</v>
+        <v>1.8152</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8434</v>
+        <v>2.4621</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8399</v>
+        <v>-0.6468</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6002</v>
+        <v>0.5587</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6632</v>
+        <v>0.3905</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.063</v>
+        <v>0.1682</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1883</v>
+        <v>2.7511</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1491</v>
+        <v>1.5542</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0392</v>
+        <v>1.1969</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5881</v>
+        <v>-2.1924</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4859</v>
+        <v>-1.1637</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1022</v>
+        <v>-1.0287</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8266</v>
+        <v>-0.4084</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2577</v>
+        <v>-0.2891</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0843</v>
+        <v>-0.1193</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. PALAZUELOS PEREZ</t>
+          <t>P. UNIACKE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8073</v>
+        <v>1.8059</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0334</v>
+        <v>3.4148</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2261</v>
+        <v>-1.6089</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5587</v>
+        <v>0.6002</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3905</v>
+        <v>1.6632</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1682</v>
+        <v>-1.063</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7511</v>
+        <v>2.1883</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5542</v>
+        <v>2.1491</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1969</v>
+        <v>0.0392</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1924</v>
+        <v>-1.5881</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1637</v>
+        <v>-0.4859</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0287</v>
+        <v>-1.1022</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4164</v>
+        <v>-1.0243</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7177</v>
+        <v>-0.171</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6987</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1077</v>
+        <v>0.7633</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5973</v>
+        <v>2.0259</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4896</v>
+        <v>-1.2626</v>
       </c>
       <c r="G17" t="n">
         <v>0.4889</v>
@@ -1780,13 +1780,13 @@
         <v>2.2893</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2969</v>
+        <v>-0.6413</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9786</v>
+        <v>-0.55</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3183</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>0.7076</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2434</v>
+        <v>-0.6427</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1373</v>
+        <v>0.7087</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3807</v>
+        <v>-1.3514</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6916</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4482</v>
+        <v>0.0489</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7144</v>
+        <v>0.2857</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2662</v>
+        <v>-0.2368</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8808</v>
+        <v>-0.7458</v>
       </c>
       <c r="E19" t="n">
         <v>-0.3624</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5184</v>
+        <v>-0.3833</v>
       </c>
       <c r="G19" t="n">
         <v>-1.9927</v>
@@ -1936,13 +1936,13 @@
         <v>1.8731</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0743</v>
+        <v>0.0607</v>
       </c>
       <c r="T19" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0058</v>
+        <v>0.1292</v>
       </c>
       <c r="V19" t="n">
         <v>0.3538</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9713</v>
+        <v>-1.8348</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2146</v>
+        <v>-0.1075</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7567</v>
+        <v>-1.7273</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9873</v>
@@ -2014,13 +2014,13 @@
         <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9434</v>
+        <v>-0.8069</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4567</v>
+        <v>-0.3495</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4867</v>
+        <v>-0.4573</v>
       </c>
       <c r="V20" t="n">
         <v>1.1675</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8398</v>
+        <v>-4.766</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3165</v>
+        <v>-1.2093</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5233</v>
+        <v>-3.5566</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0907</v>
@@ -2092,13 +2092,13 @@
         <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1299</v>
+        <v>-1.0561</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.48</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.576</v>
       </c>
       <c r="V21" t="n">
         <v>1.7513</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3.1608</v>
+        <v>5.303700000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>17.6743</v>
+        <v>17.6744</v>
       </c>
       <c r="F22" t="n">
-        <v>-14.5134</v>
+        <v>-12.3704</v>
       </c>
       <c r="G22" t="n">
         <v>5.572500000000001</v>
@@ -2170,13 +2170,13 @@
         <v>12.4872</v>
       </c>
       <c r="S22" t="n">
-        <v>-7.205600000000001</v>
+        <v>-5.0627</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.2999</v>
+        <v>-2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.905799999999999</v>
+        <v>-2.7625</v>
       </c>
       <c r="V22" t="n">
         <v>4.793900000000001</v>
